--- a/Semana 5/20250915_04_registro-de-impedimentos.xlsx
+++ b/Semana 5/20250915_04_registro-de-impedimentos.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\estudiantehyo\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nicolas\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E1307D2-5B64-478F-8F3E-4433AFCDEC02}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12330"/>
   </bookViews>
   <sheets>
     <sheet name="Impedimentos" sheetId="1" r:id="rId1"/>
@@ -24,13 +23,13 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>.</author>
     <author>Hector Bravo</author>
   </authors>
   <commentList>
-    <comment ref="B7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="B7" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -43,7 +42,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="E7" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -59,7 +58,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H7" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="H7" authorId="1" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -91,7 +90,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="53">
   <si>
     <t>Fecha de Registro</t>
   </si>
@@ -176,49 +175,100 @@
     <t>TOVAR PAYANO, Diego Marc</t>
   </si>
   <si>
-    <t>20/09/2025</t>
-  </si>
-  <si>
-    <t>Se tuvieron complicaciones durante el desarrollo de la primera historia de usuairo</t>
-  </si>
-  <si>
-    <t>Diego tiene problemas con el software jira, los datos registrados no se guardan correctamente</t>
-  </si>
-  <si>
-    <t>23/09/2025</t>
-  </si>
-  <si>
-    <t>Admistrativo</t>
-  </si>
-  <si>
-    <t>Baja</t>
-  </si>
-  <si>
     <t>Alta</t>
   </si>
   <si>
-    <t>NARVAEZ OJEDA, Carlos Andres</t>
-  </si>
-  <si>
     <t>Cerrado</t>
   </si>
   <si>
-    <t>Abierto</t>
-  </si>
-  <si>
-    <t>30/09/2025</t>
-  </si>
-  <si>
-    <t>Fallas en el software</t>
-  </si>
-  <si>
-    <t>Fallas en la codificacion</t>
+    <t>1</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>El feedback indicó rehacer toda la documentación (casos de uso, historias de usuario, diagramas), lo que consumió tiempo que estaba destinado al desarrollo.</t>
+  </si>
+  <si>
+    <t>Solo se tuvo una semana para rehacer el proyecto completo, lo que generó sobrecarga de trabajo y estrés en el equipo.</t>
+  </si>
+  <si>
+    <t>La nueva estructura del proyecto generó fallos al integrar el frontend con el backend, afectando la demostración interna.</t>
+  </si>
+  <si>
+    <t>El poco tiempo causó confusión en la asignación de tareas y retrabajo en algunas funciones.</t>
+  </si>
+  <si>
+    <t>Media</t>
+  </si>
+  <si>
+    <t>02/10/2025</t>
+  </si>
+  <si>
+    <t>03/10/2025</t>
+  </si>
+  <si>
+    <t>04/10/2025</t>
+  </si>
+  <si>
+    <t>06/10/2025</t>
+  </si>
+  <si>
+    <t>05/10/2025</t>
+  </si>
+  <si>
+    <t>Se redefinió el stack tecnológico y se reasignaron tareas para continuar el desarrollo.</t>
+  </si>
+  <si>
+    <t>Se dividió el trabajo de documentación entre miembros del equipo para completar antes de iniciar el nuevo desarrollo.</t>
+  </si>
+  <si>
+    <t>Se solucionó configurando correctamente Maven y las versiones de JDK.</t>
+  </si>
+  <si>
+    <t>Se priorizaron historias de usuario críticas y se ajustó el alcance del sprint.</t>
+  </si>
+  <si>
+    <t>Se realizaron pruebas conjuntas y ajustes en los endpoints.</t>
+  </si>
+  <si>
+    <t>Se mejoró la comunicación mediante reuniones diarias cortas.</t>
+  </si>
+  <si>
+    <t>Se tuvo que cambiar el lenguaje de programación, lo que obligó a rehacer toda la lógica del sistema y afectó significativamente el avance del proyecto.</t>
+  </si>
+  <si>
+    <t>Problemas al configurar el entorno de desarrollo en Spring  y ajustar dependencias, lo que retrasó el inicio del desarrollo del backend</t>
+  </si>
+  <si>
+    <t>=INDEX({"DIEGO MARC TOVAR PAYANO","BRITNEY ELIZABETH TORRES SANABRIA","BRITNEY ELIZABETH TORRES SANABRIA","CARLOS ENRIQUE ALEJANDRO PAUCARCHUCO","NICOLAS FISHER HERMOZA VILLAVICENCIO"},RANDBETWEEN(1,5))</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mmmm\ d\,\ yyyy"/>
   </numFmts>
@@ -353,7 +403,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="33">
+  <borders count="31">
     <border>
       <left/>
       <right/>
@@ -404,21 +454,6 @@
       <left style="hair">
         <color indexed="62"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="hair">
-        <color indexed="62"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="hair">
-        <color indexed="62"/>
-      </left>
       <right style="hair">
         <color indexed="62"/>
       </right>
@@ -556,19 +591,6 @@
       </top>
       <bottom style="thin">
         <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="hair">
-        <color indexed="62"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="hair">
-        <color indexed="62"/>
       </bottom>
       <diagonal/>
     </border>
@@ -761,7 +783,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -796,118 +818,102 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -918,51 +924,39 @@
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="11" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
@@ -972,59 +966,74 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="5" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="5" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="10" fillId="5" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="5" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="3" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="8" fillId="3" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="8" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1458,7 +1467,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -1477,837 +1486,891 @@
     <col min="12" max="256" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:10" s="57" customFormat="1" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="58"/>
-      <c r="D1" s="59"/>
-      <c r="E1" s="59"/>
-      <c r="F1" s="59"/>
-      <c r="G1" s="59"/>
-      <c r="H1" s="59"/>
-      <c r="I1" s="60"/>
+    <row r="1" spans="2:10" s="50" customFormat="1" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="51"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="52"/>
+      <c r="G1" s="52"/>
+      <c r="H1" s="52"/>
+      <c r="I1" s="53"/>
     </row>
     <row r="2" spans="2:10" s="5" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="68" t="s">
+      <c r="B2" s="61" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="69"/>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69"/>
-      <c r="F2" s="69"/>
-      <c r="G2" s="69"/>
-      <c r="H2" s="69"/>
-      <c r="I2" s="69"/>
-      <c r="J2" s="70"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="62"/>
+      <c r="E2" s="62"/>
+      <c r="F2" s="62"/>
+      <c r="G2" s="62"/>
+      <c r="H2" s="62"/>
+      <c r="I2" s="62"/>
+      <c r="J2" s="63"/>
     </row>
     <row r="3" spans="2:10" s="10" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="77" t="s">
+      <c r="B3" s="70" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="78"/>
-      <c r="D3" s="56" t="s">
+      <c r="C3" s="71"/>
+      <c r="D3" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="74"/>
-      <c r="F3" s="75"/>
-      <c r="G3" s="75"/>
-      <c r="H3" s="75"/>
-      <c r="I3" s="75"/>
-      <c r="J3" s="76"/>
+      <c r="E3" s="67"/>
+      <c r="F3" s="68"/>
+      <c r="G3" s="68"/>
+      <c r="H3" s="68"/>
+      <c r="I3" s="68"/>
+      <c r="J3" s="69"/>
     </row>
     <row r="4" spans="2:10" s="10" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="77" t="s">
+      <c r="B4" s="70" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="78"/>
-      <c r="D4" s="56" t="s">
+      <c r="C4" s="71"/>
+      <c r="D4" s="49" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="74"/>
-      <c r="F4" s="75"/>
-      <c r="G4" s="75"/>
-      <c r="H4" s="75"/>
-      <c r="I4" s="75"/>
-      <c r="J4" s="76"/>
+      <c r="E4" s="67"/>
+      <c r="F4" s="68"/>
+      <c r="G4" s="68"/>
+      <c r="H4" s="68"/>
+      <c r="I4" s="68"/>
+      <c r="J4" s="69"/>
     </row>
     <row r="5" spans="2:10" s="10" customFormat="1" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="71"/>
-      <c r="C5" s="72"/>
-      <c r="D5" s="72"/>
-      <c r="E5" s="72"/>
-      <c r="F5" s="72"/>
-      <c r="G5" s="72"/>
-      <c r="H5" s="72"/>
-      <c r="I5" s="72"/>
-      <c r="J5" s="73"/>
+      <c r="B5" s="64"/>
+      <c r="C5" s="65"/>
+      <c r="D5" s="65"/>
+      <c r="E5" s="65"/>
+      <c r="F5" s="65"/>
+      <c r="G5" s="65"/>
+      <c r="H5" s="65"/>
+      <c r="I5" s="65"/>
+      <c r="J5" s="66"/>
     </row>
     <row r="6" spans="2:10" s="11" customFormat="1" ht="50.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="63" t="s">
+      <c r="B6" s="56" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="64"/>
-      <c r="D6" s="65"/>
-      <c r="E6" s="65"/>
-      <c r="F6" s="65"/>
-      <c r="G6" s="62"/>
-      <c r="H6" s="66"/>
-      <c r="I6" s="66"/>
-      <c r="J6" s="67"/>
+      <c r="C6" s="57"/>
+      <c r="D6" s="58"/>
+      <c r="E6" s="58"/>
+      <c r="F6" s="58"/>
+      <c r="G6" s="55"/>
+      <c r="H6" s="59"/>
+      <c r="I6" s="59"/>
+      <c r="J6" s="60"/>
     </row>
     <row r="7" spans="2:10" s="9" customFormat="1" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="61" t="s">
+      <c r="B7" s="54" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="61" t="s">
+      <c r="C7" s="54" t="s">
         <v>0</v>
       </c>
-      <c r="D7" s="61" t="s">
+      <c r="D7" s="54" t="s">
         <v>17</v>
       </c>
-      <c r="E7" s="61" t="s">
+      <c r="E7" s="54" t="s">
         <v>7</v>
       </c>
-      <c r="F7" s="61" t="s">
+      <c r="F7" s="54" t="s">
         <v>1</v>
       </c>
-      <c r="G7" s="61" t="s">
+      <c r="G7" s="54" t="s">
         <v>3</v>
       </c>
-      <c r="H7" s="61" t="s">
+      <c r="H7" s="54" t="s">
         <v>8</v>
       </c>
-      <c r="I7" s="61" t="s">
+      <c r="I7" s="54" t="s">
         <v>2</v>
       </c>
-      <c r="J7" s="61" t="s">
+      <c r="J7" s="54" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="2:10" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="B8" s="39" t="s">
+    <row r="8" spans="2:10" ht="280.5" x14ac:dyDescent="0.2">
+      <c r="B8" s="34" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="72">
+        <v>45930</v>
+      </c>
+      <c r="D8" s="73" t="s">
+        <v>50</v>
+      </c>
+      <c r="E8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F8" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="G8" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="H8" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="I8" s="74">
+        <v>45932</v>
+      </c>
+      <c r="J8" s="14" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="9" spans="2:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="B9" s="35" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="72">
+        <v>45930</v>
+      </c>
+      <c r="D9" s="73" t="s">
+        <v>34</v>
+      </c>
+      <c r="E9" t="s">
+        <v>38</v>
+      </c>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="H9" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="I9" s="76">
+        <v>45933</v>
+      </c>
+      <c r="J9" s="18" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10" spans="2:10" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="B10" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="49" t="s">
+      <c r="C10" s="72">
+        <v>45931</v>
+      </c>
+      <c r="D10" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="E10" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="13" t="s">
+      <c r="F10" s="16"/>
+      <c r="G10" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="H10" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="E8" s="12" t="s">
+      <c r="I10" s="75">
+        <v>45934</v>
+      </c>
+      <c r="J10" s="18" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="11" spans="2:10" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="B11" s="36" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" s="72">
+        <v>45931</v>
+      </c>
+      <c r="D11" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F11" s="16"/>
+      <c r="G11" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="H11" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="I11" s="75">
+        <v>45936</v>
+      </c>
+      <c r="J11" s="18" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="B12" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="F8" s="13" t="s">
+      <c r="C12" s="72">
+        <v>45933</v>
+      </c>
+      <c r="D12" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="E12" t="s">
+        <v>38</v>
+      </c>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="H12" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="I12" s="75">
+        <v>45935</v>
+      </c>
+      <c r="J12" s="18" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="13" spans="2:10" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="B13" s="36" t="s">
         <v>30</v>
       </c>
-      <c r="G8" s="13" t="s">
+      <c r="C13" s="72">
+        <v>45932</v>
+      </c>
+      <c r="D13" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="E13" t="s">
+        <v>38</v>
+      </c>
+      <c r="F13" s="16"/>
+      <c r="G13" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="H13" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="I13" s="75">
+        <v>45935</v>
+      </c>
+      <c r="J13" s="18" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="14" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B14" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" s="44"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="16"/>
+      <c r="G14" s="16"/>
+      <c r="H14" s="15"/>
+      <c r="I14" s="17"/>
+      <c r="J14" s="18"/>
+    </row>
+    <row r="15" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B15" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" s="44"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="16"/>
+      <c r="G15" s="16"/>
+      <c r="H15" s="15"/>
+      <c r="I15" s="17"/>
+      <c r="J15" s="18"/>
+    </row>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B16" s="36" t="s">
         <v>33</v>
       </c>
-      <c r="H8" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="I8" s="14">
-        <v>45923</v>
-      </c>
-      <c r="J8" s="15" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="9" spans="2:10" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="B9" s="40" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" s="50" t="s">
-        <v>26</v>
-      </c>
-      <c r="D9" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="E9" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="F9" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="G9" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="H9" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="I9" s="18"/>
-      <c r="J9" s="19" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B10" s="40"/>
-      <c r="C10" s="50"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="16"/>
-      <c r="F10" s="17"/>
-      <c r="G10" s="17"/>
-      <c r="H10" s="16"/>
-      <c r="I10" s="18"/>
-      <c r="J10" s="19"/>
-    </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B11" s="41"/>
-      <c r="C11" s="51"/>
-      <c r="D11" s="21"/>
-      <c r="E11" s="20"/>
-      <c r="F11" s="21"/>
-      <c r="G11" s="21"/>
-      <c r="H11" s="20"/>
-      <c r="I11" s="22"/>
-      <c r="J11" s="23"/>
-    </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B12" s="41"/>
-      <c r="C12" s="51"/>
-      <c r="D12" s="21"/>
-      <c r="E12" s="20"/>
-      <c r="F12" s="21"/>
-      <c r="G12" s="21"/>
-      <c r="H12" s="20"/>
-      <c r="I12" s="22"/>
-      <c r="J12" s="23"/>
-    </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B13" s="41"/>
-      <c r="C13" s="51"/>
-      <c r="D13" s="21"/>
-      <c r="E13" s="20"/>
-      <c r="F13" s="21"/>
-      <c r="G13" s="21"/>
-      <c r="H13" s="20"/>
-      <c r="I13" s="22"/>
-      <c r="J13" s="23"/>
-    </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B14" s="41"/>
-      <c r="C14" s="51"/>
-      <c r="D14" s="21"/>
-      <c r="E14" s="20"/>
-      <c r="F14" s="21"/>
-      <c r="G14" s="21"/>
-      <c r="H14" s="20"/>
-      <c r="I14" s="22"/>
-      <c r="J14" s="23"/>
-    </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B15" s="41"/>
-      <c r="C15" s="51"/>
-      <c r="D15" s="21"/>
-      <c r="E15" s="20"/>
-      <c r="F15" s="21"/>
-      <c r="G15" s="21"/>
-      <c r="H15" s="20"/>
-      <c r="I15" s="22"/>
-      <c r="J15" s="23"/>
-    </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B16" s="41"/>
-      <c r="C16" s="51"/>
-      <c r="D16" s="21"/>
-      <c r="E16" s="20"/>
-      <c r="F16" s="21"/>
-      <c r="G16" s="21"/>
-      <c r="H16" s="20"/>
-      <c r="I16" s="22"/>
-      <c r="J16" s="23"/>
+      <c r="C16" s="44"/>
+      <c r="D16" s="16"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="16"/>
+      <c r="G16" s="16"/>
+      <c r="H16" s="15"/>
+      <c r="I16" s="17"/>
+      <c r="J16" s="18"/>
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B17" s="41"/>
-      <c r="C17" s="51"/>
-      <c r="D17" s="21"/>
-      <c r="E17" s="20"/>
-      <c r="F17" s="21"/>
-      <c r="G17" s="21"/>
-      <c r="H17" s="20"/>
-      <c r="I17" s="22"/>
-      <c r="J17" s="23"/>
+      <c r="B17" s="36"/>
+      <c r="C17" s="44"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="16"/>
+      <c r="G17" s="16"/>
+      <c r="H17" s="15"/>
+      <c r="I17" s="17"/>
+      <c r="J17" s="18"/>
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B18" s="41"/>
-      <c r="C18" s="51"/>
-      <c r="D18" s="21"/>
-      <c r="E18" s="20"/>
-      <c r="F18" s="21"/>
-      <c r="G18" s="21"/>
-      <c r="H18" s="20"/>
-      <c r="I18" s="22"/>
-      <c r="J18" s="23"/>
+      <c r="B18" s="36"/>
+      <c r="C18" s="44"/>
+      <c r="D18" s="16"/>
+      <c r="E18" s="15"/>
+      <c r="F18" s="16"/>
+      <c r="G18" s="16"/>
+      <c r="H18" s="15"/>
+      <c r="I18" s="17"/>
+      <c r="J18" s="18"/>
     </row>
     <row r="19" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B19" s="41"/>
-      <c r="C19" s="51"/>
-      <c r="D19" s="21"/>
-      <c r="E19" s="20"/>
-      <c r="F19" s="21"/>
-      <c r="G19" s="21"/>
-      <c r="H19" s="20"/>
-      <c r="I19" s="22"/>
-      <c r="J19" s="23"/>
+      <c r="B19" s="36"/>
+      <c r="C19" s="45"/>
+      <c r="D19" s="16"/>
+      <c r="E19" s="19"/>
+      <c r="F19" s="20"/>
+      <c r="G19" s="20"/>
+      <c r="H19" s="19"/>
+      <c r="I19" s="21"/>
+      <c r="J19" s="22"/>
     </row>
     <row r="20" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B20" s="41"/>
-      <c r="C20" s="51"/>
-      <c r="D20" s="21"/>
-      <c r="E20" s="20"/>
-      <c r="F20" s="21"/>
-      <c r="G20" s="21"/>
-      <c r="H20" s="20"/>
-      <c r="I20" s="22"/>
-      <c r="J20" s="23"/>
+      <c r="B20" s="36"/>
+      <c r="C20" s="45"/>
+      <c r="D20" s="16"/>
+      <c r="E20" s="19"/>
+      <c r="F20" s="20"/>
+      <c r="G20" s="20"/>
+      <c r="H20" s="19"/>
+      <c r="I20" s="21"/>
+      <c r="J20" s="22"/>
     </row>
     <row r="21" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B21" s="42"/>
-      <c r="C21" s="52"/>
-      <c r="D21" s="21"/>
-      <c r="E21" s="24"/>
-      <c r="F21" s="25"/>
-      <c r="G21" s="25"/>
-      <c r="H21" s="24"/>
-      <c r="I21" s="26"/>
-      <c r="J21" s="27"/>
+      <c r="B21" s="37"/>
+      <c r="C21" s="45"/>
+      <c r="D21" s="16"/>
+      <c r="E21" s="19"/>
+      <c r="F21" s="20"/>
+      <c r="G21" s="20"/>
+      <c r="H21" s="19"/>
+      <c r="I21" s="21"/>
+      <c r="J21" s="22"/>
     </row>
     <row r="22" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B22" s="42"/>
-      <c r="C22" s="52"/>
-      <c r="D22" s="21"/>
-      <c r="E22" s="24"/>
-      <c r="F22" s="25"/>
-      <c r="G22" s="25"/>
-      <c r="H22" s="24"/>
-      <c r="I22" s="26"/>
-      <c r="J22" s="27"/>
+      <c r="B22" s="37"/>
+      <c r="C22" s="45"/>
+      <c r="D22" s="16"/>
+      <c r="E22" s="19"/>
+      <c r="F22" s="20"/>
+      <c r="G22" s="20"/>
+      <c r="H22" s="19"/>
+      <c r="I22" s="21"/>
+      <c r="J22" s="22"/>
     </row>
     <row r="23" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B23" s="42"/>
-      <c r="C23" s="52"/>
-      <c r="D23" s="21"/>
-      <c r="E23" s="24"/>
-      <c r="F23" s="25"/>
-      <c r="G23" s="25"/>
-      <c r="H23" s="24"/>
-      <c r="I23" s="26"/>
-      <c r="J23" s="27"/>
+      <c r="B23" s="37"/>
+      <c r="C23" s="45"/>
+      <c r="D23" s="16"/>
+      <c r="E23" s="19"/>
+      <c r="F23" s="20"/>
+      <c r="G23" s="20"/>
+      <c r="H23" s="19"/>
+      <c r="I23" s="21"/>
+      <c r="J23" s="22"/>
     </row>
     <row r="24" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B24" s="42"/>
-      <c r="C24" s="52"/>
-      <c r="D24" s="21"/>
-      <c r="E24" s="24"/>
-      <c r="F24" s="25"/>
-      <c r="G24" s="25"/>
-      <c r="H24" s="24"/>
-      <c r="I24" s="26"/>
-      <c r="J24" s="27"/>
+      <c r="B24" s="37"/>
+      <c r="C24" s="45"/>
+      <c r="D24" s="16"/>
+      <c r="E24" s="19"/>
+      <c r="F24" s="20"/>
+      <c r="G24" s="20"/>
+      <c r="H24" s="19"/>
+      <c r="I24" s="21"/>
+      <c r="J24" s="22"/>
     </row>
     <row r="25" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B25" s="42"/>
-      <c r="C25" s="52"/>
-      <c r="D25" s="21"/>
-      <c r="E25" s="24"/>
-      <c r="F25" s="25"/>
-      <c r="G25" s="25"/>
-      <c r="H25" s="24"/>
-      <c r="I25" s="26"/>
-      <c r="J25" s="27"/>
+      <c r="B25" s="37"/>
+      <c r="C25" s="45"/>
+      <c r="D25" s="16"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="20"/>
+      <c r="G25" s="20"/>
+      <c r="H25" s="19"/>
+      <c r="I25" s="21"/>
+      <c r="J25" s="22"/>
     </row>
     <row r="26" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B26" s="42"/>
-      <c r="C26" s="52"/>
-      <c r="D26" s="21"/>
-      <c r="E26" s="24"/>
-      <c r="F26" s="25"/>
-      <c r="G26" s="25"/>
-      <c r="H26" s="24"/>
-      <c r="I26" s="26"/>
-      <c r="J26" s="27"/>
+      <c r="B26" s="37"/>
+      <c r="C26" s="45"/>
+      <c r="D26" s="16"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="20"/>
+      <c r="G26" s="20"/>
+      <c r="H26" s="19"/>
+      <c r="I26" s="21"/>
+      <c r="J26" s="22"/>
     </row>
     <row r="27" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B27" s="42"/>
-      <c r="C27" s="52"/>
-      <c r="D27" s="21"/>
-      <c r="E27" s="24"/>
-      <c r="F27" s="25"/>
-      <c r="G27" s="25"/>
-      <c r="H27" s="24"/>
-      <c r="I27" s="26"/>
-      <c r="J27" s="27"/>
+      <c r="B27" s="37"/>
+      <c r="C27" s="46"/>
+      <c r="D27" s="16"/>
+      <c r="E27" s="41"/>
+      <c r="F27" s="23"/>
+      <c r="G27" s="23"/>
+      <c r="H27" s="41"/>
+      <c r="I27" s="24"/>
+      <c r="J27" s="25"/>
     </row>
     <row r="28" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B28" s="42"/>
-      <c r="C28" s="52"/>
-      <c r="D28" s="21"/>
-      <c r="E28" s="24"/>
-      <c r="F28" s="25"/>
-      <c r="G28" s="25"/>
-      <c r="H28" s="24"/>
-      <c r="I28" s="26"/>
-      <c r="J28" s="27"/>
+      <c r="B28" s="37"/>
+      <c r="C28" s="46"/>
+      <c r="D28" s="16"/>
+      <c r="E28" s="41"/>
+      <c r="F28" s="23"/>
+      <c r="G28" s="23"/>
+      <c r="H28" s="41"/>
+      <c r="I28" s="24"/>
+      <c r="J28" s="25"/>
     </row>
     <row r="29" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B29" s="43"/>
-      <c r="C29" s="53"/>
-      <c r="D29" s="21"/>
-      <c r="E29" s="46"/>
-      <c r="F29" s="28"/>
-      <c r="G29" s="28"/>
-      <c r="H29" s="46"/>
-      <c r="I29" s="29"/>
-      <c r="J29" s="30"/>
+      <c r="B29" s="38"/>
+      <c r="C29" s="46"/>
+      <c r="D29" s="16"/>
+      <c r="E29" s="41"/>
+      <c r="F29" s="23"/>
+      <c r="G29" s="23"/>
+      <c r="H29" s="41"/>
+      <c r="I29" s="24"/>
+      <c r="J29" s="25"/>
     </row>
     <row r="30" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B30" s="43"/>
-      <c r="C30" s="53"/>
-      <c r="D30" s="21"/>
-      <c r="E30" s="46"/>
-      <c r="F30" s="28"/>
-      <c r="G30" s="28"/>
-      <c r="H30" s="46"/>
-      <c r="I30" s="29"/>
-      <c r="J30" s="30"/>
+      <c r="B30" s="38"/>
+      <c r="C30" s="46"/>
+      <c r="D30" s="16"/>
+      <c r="E30" s="41"/>
+      <c r="F30" s="23"/>
+      <c r="G30" s="23"/>
+      <c r="H30" s="41"/>
+      <c r="I30" s="24"/>
+      <c r="J30" s="25"/>
     </row>
     <row r="31" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B31" s="43"/>
-      <c r="C31" s="53"/>
-      <c r="D31" s="21"/>
-      <c r="E31" s="46"/>
-      <c r="F31" s="28"/>
-      <c r="G31" s="28"/>
-      <c r="H31" s="46"/>
-      <c r="I31" s="29"/>
-      <c r="J31" s="30"/>
+      <c r="B31" s="38"/>
+      <c r="C31" s="46"/>
+      <c r="D31" s="16"/>
+      <c r="E31" s="41"/>
+      <c r="F31" s="23"/>
+      <c r="G31" s="23"/>
+      <c r="H31" s="41"/>
+      <c r="I31" s="24"/>
+      <c r="J31" s="25"/>
     </row>
     <row r="32" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B32" s="43"/>
-      <c r="C32" s="53"/>
-      <c r="D32" s="21"/>
-      <c r="E32" s="46"/>
-      <c r="F32" s="28"/>
-      <c r="G32" s="28"/>
-      <c r="H32" s="46"/>
-      <c r="I32" s="29"/>
-      <c r="J32" s="30"/>
+      <c r="B32" s="38"/>
+      <c r="C32" s="46"/>
+      <c r="D32" s="16"/>
+      <c r="E32" s="41"/>
+      <c r="F32" s="23"/>
+      <c r="G32" s="23"/>
+      <c r="H32" s="41"/>
+      <c r="I32" s="24"/>
+      <c r="J32" s="25"/>
     </row>
     <row r="33" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B33" s="43"/>
-      <c r="C33" s="53"/>
-      <c r="D33" s="21"/>
-      <c r="E33" s="46"/>
-      <c r="F33" s="28"/>
-      <c r="G33" s="28"/>
-      <c r="H33" s="46"/>
-      <c r="I33" s="29"/>
-      <c r="J33" s="30"/>
+      <c r="B33" s="38"/>
+      <c r="C33" s="46"/>
+      <c r="D33" s="16"/>
+      <c r="E33" s="41"/>
+      <c r="F33" s="23"/>
+      <c r="G33" s="23"/>
+      <c r="H33" s="41"/>
+      <c r="I33" s="24"/>
+      <c r="J33" s="25"/>
     </row>
     <row r="34" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B34" s="43"/>
-      <c r="C34" s="53"/>
-      <c r="D34" s="21"/>
-      <c r="E34" s="46"/>
-      <c r="F34" s="28"/>
-      <c r="G34" s="28"/>
-      <c r="H34" s="46"/>
-      <c r="I34" s="29"/>
-      <c r="J34" s="30"/>
+      <c r="B34" s="38"/>
+      <c r="C34" s="46"/>
+      <c r="D34" s="16"/>
+      <c r="E34" s="41"/>
+      <c r="F34" s="23"/>
+      <c r="G34" s="23"/>
+      <c r="H34" s="41"/>
+      <c r="I34" s="24"/>
+      <c r="J34" s="25"/>
     </row>
     <row r="35" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B35" s="43"/>
-      <c r="C35" s="53"/>
-      <c r="D35" s="21"/>
-      <c r="E35" s="46"/>
-      <c r="F35" s="28"/>
-      <c r="G35" s="28"/>
-      <c r="H35" s="46"/>
-      <c r="I35" s="29"/>
-      <c r="J35" s="30"/>
+      <c r="B35" s="38"/>
+      <c r="C35" s="46"/>
+      <c r="D35" s="16"/>
+      <c r="E35" s="41"/>
+      <c r="F35" s="23"/>
+      <c r="G35" s="23"/>
+      <c r="H35" s="41"/>
+      <c r="I35" s="24"/>
+      <c r="J35" s="25"/>
     </row>
     <row r="36" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B36" s="43"/>
-      <c r="C36" s="53"/>
-      <c r="D36" s="21"/>
-      <c r="E36" s="46"/>
-      <c r="F36" s="28"/>
-      <c r="G36" s="28"/>
-      <c r="H36" s="46"/>
-      <c r="I36" s="29"/>
-      <c r="J36" s="30"/>
+      <c r="B36" s="38"/>
+      <c r="C36" s="46"/>
+      <c r="D36" s="16"/>
+      <c r="E36" s="41"/>
+      <c r="F36" s="23"/>
+      <c r="G36" s="23"/>
+      <c r="H36" s="41"/>
+      <c r="I36" s="24"/>
+      <c r="J36" s="25"/>
     </row>
     <row r="37" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B37" s="43"/>
-      <c r="C37" s="53"/>
-      <c r="D37" s="21"/>
-      <c r="E37" s="46"/>
-      <c r="F37" s="28"/>
-      <c r="G37" s="28"/>
-      <c r="H37" s="46"/>
-      <c r="I37" s="29"/>
-      <c r="J37" s="30"/>
+      <c r="B37" s="38"/>
+      <c r="C37" s="46"/>
+      <c r="D37" s="16"/>
+      <c r="E37" s="41"/>
+      <c r="F37" s="23"/>
+      <c r="G37" s="23"/>
+      <c r="H37" s="41"/>
+      <c r="I37" s="24"/>
+      <c r="J37" s="25"/>
     </row>
     <row r="38" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B38" s="43"/>
-      <c r="C38" s="53"/>
-      <c r="D38" s="21"/>
-      <c r="E38" s="46"/>
-      <c r="F38" s="28"/>
-      <c r="G38" s="28"/>
-      <c r="H38" s="46"/>
-      <c r="I38" s="29"/>
-      <c r="J38" s="30"/>
+      <c r="B38" s="38"/>
+      <c r="C38" s="46"/>
+      <c r="D38" s="16"/>
+      <c r="E38" s="41"/>
+      <c r="F38" s="23"/>
+      <c r="G38" s="23"/>
+      <c r="H38" s="41"/>
+      <c r="I38" s="24"/>
+      <c r="J38" s="25"/>
     </row>
     <row r="39" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B39" s="43"/>
-      <c r="C39" s="53"/>
-      <c r="D39" s="21"/>
-      <c r="E39" s="46"/>
-      <c r="F39" s="28"/>
-      <c r="G39" s="28"/>
-      <c r="H39" s="46"/>
-      <c r="I39" s="29"/>
-      <c r="J39" s="30"/>
+      <c r="B39" s="38"/>
+      <c r="C39" s="46"/>
+      <c r="D39" s="16"/>
+      <c r="E39" s="41"/>
+      <c r="F39" s="23"/>
+      <c r="G39" s="23"/>
+      <c r="H39" s="41"/>
+      <c r="I39" s="24"/>
+      <c r="J39" s="25"/>
     </row>
     <row r="40" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B40" s="43"/>
-      <c r="C40" s="53"/>
-      <c r="D40" s="21"/>
-      <c r="E40" s="46"/>
-      <c r="F40" s="28"/>
-      <c r="G40" s="28"/>
-      <c r="H40" s="46"/>
-      <c r="I40" s="29"/>
-      <c r="J40" s="30"/>
+      <c r="B40" s="38"/>
+      <c r="C40" s="46"/>
+      <c r="D40" s="16"/>
+      <c r="E40" s="41"/>
+      <c r="F40" s="23"/>
+      <c r="G40" s="23"/>
+      <c r="H40" s="41"/>
+      <c r="I40" s="24"/>
+      <c r="J40" s="25"/>
     </row>
     <row r="41" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B41" s="43"/>
-      <c r="C41" s="53"/>
-      <c r="D41" s="21"/>
-      <c r="E41" s="46"/>
-      <c r="F41" s="28"/>
-      <c r="G41" s="28"/>
-      <c r="H41" s="46"/>
-      <c r="I41" s="29"/>
-      <c r="J41" s="30"/>
+      <c r="B41" s="38"/>
+      <c r="C41" s="46"/>
+      <c r="D41" s="16"/>
+      <c r="E41" s="41"/>
+      <c r="F41" s="23"/>
+      <c r="G41" s="23"/>
+      <c r="H41" s="41"/>
+      <c r="I41" s="24"/>
+      <c r="J41" s="25"/>
     </row>
     <row r="42" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B42" s="43"/>
-      <c r="C42" s="53"/>
-      <c r="D42" s="21"/>
-      <c r="E42" s="46"/>
-      <c r="F42" s="28"/>
-      <c r="G42" s="28"/>
-      <c r="H42" s="46"/>
-      <c r="I42" s="29"/>
-      <c r="J42" s="30"/>
+      <c r="B42" s="38"/>
+      <c r="C42" s="46"/>
+      <c r="D42" s="16"/>
+      <c r="E42" s="41"/>
+      <c r="F42" s="23"/>
+      <c r="G42" s="23"/>
+      <c r="H42" s="41"/>
+      <c r="I42" s="24"/>
+      <c r="J42" s="25"/>
     </row>
     <row r="43" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B43" s="43"/>
-      <c r="C43" s="53"/>
-      <c r="D43" s="21"/>
-      <c r="E43" s="46"/>
-      <c r="F43" s="28"/>
-      <c r="G43" s="28"/>
-      <c r="H43" s="46"/>
-      <c r="I43" s="29"/>
-      <c r="J43" s="30"/>
+      <c r="B43" s="38"/>
+      <c r="C43" s="46"/>
+      <c r="D43" s="16"/>
+      <c r="E43" s="41"/>
+      <c r="F43" s="23"/>
+      <c r="G43" s="23"/>
+      <c r="H43" s="41"/>
+      <c r="I43" s="24"/>
+      <c r="J43" s="25"/>
     </row>
     <row r="44" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B44" s="43"/>
-      <c r="C44" s="53"/>
-      <c r="D44" s="21"/>
-      <c r="E44" s="46"/>
-      <c r="F44" s="28"/>
-      <c r="G44" s="28"/>
-      <c r="H44" s="46"/>
-      <c r="I44" s="29"/>
-      <c r="J44" s="30"/>
+      <c r="B44" s="38"/>
+      <c r="C44" s="46"/>
+      <c r="D44" s="16"/>
+      <c r="E44" s="41"/>
+      <c r="F44" s="23"/>
+      <c r="G44" s="23"/>
+      <c r="H44" s="41"/>
+      <c r="I44" s="24"/>
+      <c r="J44" s="25"/>
     </row>
     <row r="45" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B45" s="43"/>
-      <c r="C45" s="53"/>
-      <c r="D45" s="21"/>
-      <c r="E45" s="46"/>
-      <c r="F45" s="28"/>
-      <c r="G45" s="28"/>
-      <c r="H45" s="46"/>
-      <c r="I45" s="29"/>
-      <c r="J45" s="30"/>
+      <c r="B45" s="38"/>
+      <c r="C45" s="46"/>
+      <c r="D45" s="16"/>
+      <c r="E45" s="41"/>
+      <c r="F45" s="23"/>
+      <c r="G45" s="23"/>
+      <c r="H45" s="41"/>
+      <c r="I45" s="24"/>
+      <c r="J45" s="25"/>
     </row>
     <row r="46" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B46" s="43"/>
-      <c r="C46" s="53"/>
-      <c r="D46" s="21"/>
-      <c r="E46" s="46"/>
-      <c r="F46" s="28"/>
-      <c r="G46" s="28"/>
-      <c r="H46" s="46"/>
-      <c r="I46" s="29"/>
-      <c r="J46" s="30"/>
+      <c r="B46" s="38"/>
+      <c r="C46" s="46"/>
+      <c r="D46" s="16"/>
+      <c r="E46" s="41"/>
+      <c r="F46" s="23"/>
+      <c r="G46" s="23"/>
+      <c r="H46" s="41"/>
+      <c r="I46" s="24"/>
+      <c r="J46" s="25"/>
     </row>
     <row r="47" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B47" s="43"/>
-      <c r="C47" s="53"/>
-      <c r="D47" s="21"/>
-      <c r="E47" s="46"/>
-      <c r="F47" s="28"/>
-      <c r="G47" s="28"/>
-      <c r="H47" s="46"/>
-      <c r="I47" s="29"/>
-      <c r="J47" s="30"/>
+      <c r="B47" s="38"/>
+      <c r="C47" s="46"/>
+      <c r="D47" s="16"/>
+      <c r="E47" s="41"/>
+      <c r="F47" s="23"/>
+      <c r="G47" s="23"/>
+      <c r="H47" s="41"/>
+      <c r="I47" s="24"/>
+      <c r="J47" s="25"/>
     </row>
     <row r="48" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B48" s="43"/>
-      <c r="C48" s="53"/>
-      <c r="D48" s="21"/>
-      <c r="E48" s="46"/>
-      <c r="F48" s="28"/>
-      <c r="G48" s="28"/>
-      <c r="H48" s="46"/>
-      <c r="I48" s="29"/>
-      <c r="J48" s="30"/>
+      <c r="B48" s="38"/>
+      <c r="C48" s="46"/>
+      <c r="D48" s="16"/>
+      <c r="E48" s="41"/>
+      <c r="F48" s="23"/>
+      <c r="G48" s="23"/>
+      <c r="H48" s="41"/>
+      <c r="I48" s="24"/>
+      <c r="J48" s="25"/>
     </row>
     <row r="49" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B49" s="43"/>
-      <c r="C49" s="53"/>
-      <c r="D49" s="21"/>
-      <c r="E49" s="46"/>
-      <c r="F49" s="28"/>
-      <c r="G49" s="28"/>
-      <c r="H49" s="46"/>
-      <c r="I49" s="29"/>
-      <c r="J49" s="30"/>
+      <c r="B49" s="38"/>
+      <c r="C49" s="46"/>
+      <c r="D49" s="16"/>
+      <c r="E49" s="41"/>
+      <c r="F49" s="23"/>
+      <c r="G49" s="23"/>
+      <c r="H49" s="41"/>
+      <c r="I49" s="24"/>
+      <c r="J49" s="25"/>
     </row>
     <row r="50" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B50" s="43"/>
-      <c r="C50" s="53"/>
-      <c r="D50" s="21"/>
-      <c r="E50" s="46"/>
-      <c r="F50" s="28"/>
-      <c r="G50" s="28"/>
-      <c r="H50" s="46"/>
-      <c r="I50" s="29"/>
-      <c r="J50" s="30"/>
+      <c r="B50" s="38"/>
+      <c r="C50" s="46"/>
+      <c r="D50" s="16"/>
+      <c r="E50" s="41"/>
+      <c r="F50" s="23"/>
+      <c r="G50" s="23"/>
+      <c r="H50" s="41"/>
+      <c r="I50" s="24"/>
+      <c r="J50" s="25"/>
     </row>
     <row r="51" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B51" s="43"/>
-      <c r="C51" s="53"/>
-      <c r="D51" s="21"/>
-      <c r="E51" s="46"/>
-      <c r="F51" s="28"/>
-      <c r="G51" s="28"/>
-      <c r="H51" s="46"/>
-      <c r="I51" s="29"/>
-      <c r="J51" s="30"/>
+      <c r="B51" s="38"/>
+      <c r="C51" s="46"/>
+      <c r="D51" s="16"/>
+      <c r="E51" s="41"/>
+      <c r="F51" s="23"/>
+      <c r="G51" s="23"/>
+      <c r="H51" s="41"/>
+      <c r="I51" s="24"/>
+      <c r="J51" s="25"/>
     </row>
     <row r="52" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B52" s="43"/>
-      <c r="C52" s="53"/>
-      <c r="D52" s="21"/>
-      <c r="E52" s="46"/>
-      <c r="F52" s="28"/>
-      <c r="G52" s="28"/>
-      <c r="H52" s="46"/>
-      <c r="I52" s="29"/>
-      <c r="J52" s="30"/>
+      <c r="B52" s="38"/>
+      <c r="C52" s="46"/>
+      <c r="D52" s="16"/>
+      <c r="E52" s="41"/>
+      <c r="F52" s="23"/>
+      <c r="G52" s="23"/>
+      <c r="H52" s="41"/>
+      <c r="I52" s="24"/>
+      <c r="J52" s="25"/>
     </row>
     <row r="53" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B53" s="43"/>
-      <c r="C53" s="53"/>
-      <c r="D53" s="21"/>
-      <c r="E53" s="46"/>
-      <c r="F53" s="28"/>
-      <c r="G53" s="28"/>
-      <c r="H53" s="46"/>
-      <c r="I53" s="29"/>
-      <c r="J53" s="30"/>
+      <c r="B53" s="38"/>
+      <c r="C53" s="46"/>
+      <c r="D53" s="16"/>
+      <c r="E53" s="41"/>
+      <c r="F53" s="23"/>
+      <c r="G53" s="23"/>
+      <c r="H53" s="41"/>
+      <c r="I53" s="24"/>
+      <c r="J53" s="25"/>
     </row>
     <row r="54" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B54" s="43"/>
-      <c r="C54" s="53"/>
-      <c r="D54" s="21"/>
-      <c r="E54" s="46"/>
-      <c r="F54" s="28"/>
-      <c r="G54" s="28"/>
-      <c r="H54" s="46"/>
-      <c r="I54" s="29"/>
-      <c r="J54" s="30"/>
+      <c r="B54" s="38"/>
+      <c r="C54" s="46"/>
+      <c r="D54" s="16"/>
+      <c r="E54" s="41"/>
+      <c r="F54" s="23"/>
+      <c r="G54" s="23"/>
+      <c r="H54" s="41"/>
+      <c r="I54" s="24"/>
+      <c r="J54" s="25"/>
     </row>
     <row r="55" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B55" s="43"/>
-      <c r="C55" s="53"/>
-      <c r="D55" s="21"/>
-      <c r="E55" s="46"/>
-      <c r="F55" s="28"/>
-      <c r="G55" s="28"/>
-      <c r="H55" s="46"/>
-      <c r="I55" s="29"/>
-      <c r="J55" s="30"/>
+      <c r="B55" s="38"/>
+      <c r="C55" s="46"/>
+      <c r="D55" s="16"/>
+      <c r="E55" s="41"/>
+      <c r="F55" s="23"/>
+      <c r="G55" s="23"/>
+      <c r="H55" s="41"/>
+      <c r="I55" s="24"/>
+      <c r="J55" s="25"/>
     </row>
     <row r="56" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B56" s="43"/>
-      <c r="C56" s="53"/>
-      <c r="D56" s="21"/>
-      <c r="E56" s="46"/>
-      <c r="F56" s="28"/>
-      <c r="G56" s="28"/>
-      <c r="H56" s="46"/>
-      <c r="I56" s="29"/>
-      <c r="J56" s="30"/>
+      <c r="B56" s="38"/>
+      <c r="C56" s="46"/>
+      <c r="D56" s="16"/>
+      <c r="E56" s="41"/>
+      <c r="F56" s="23"/>
+      <c r="G56" s="23"/>
+      <c r="H56" s="41"/>
+      <c r="I56" s="24"/>
+      <c r="J56" s="25"/>
     </row>
     <row r="57" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B57" s="43"/>
-      <c r="C57" s="53"/>
-      <c r="D57" s="21"/>
-      <c r="E57" s="46"/>
-      <c r="F57" s="28"/>
-      <c r="G57" s="28"/>
-      <c r="H57" s="46"/>
-      <c r="I57" s="29"/>
-      <c r="J57" s="30"/>
+      <c r="B57" s="38"/>
+      <c r="C57" s="46"/>
+      <c r="D57" s="16"/>
+      <c r="E57" s="41"/>
+      <c r="F57" s="23"/>
+      <c r="G57" s="23"/>
+      <c r="H57" s="41"/>
+      <c r="I57" s="24"/>
+      <c r="J57" s="25"/>
     </row>
     <row r="58" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B58" s="43"/>
-      <c r="C58" s="53"/>
-      <c r="D58" s="21"/>
-      <c r="E58" s="46"/>
-      <c r="F58" s="28"/>
-      <c r="G58" s="28"/>
-      <c r="H58" s="46"/>
-      <c r="I58" s="29"/>
-      <c r="J58" s="30"/>
+      <c r="B58" s="38"/>
+      <c r="C58" s="47"/>
+      <c r="D58" s="31"/>
+      <c r="E58" s="42"/>
+      <c r="F58" s="30"/>
+      <c r="G58" s="30"/>
+      <c r="H58" s="42"/>
+      <c r="I58" s="32"/>
+      <c r="J58" s="33"/>
     </row>
     <row r="59" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B59" s="43"/>
-      <c r="C59" s="53"/>
-      <c r="D59" s="21"/>
-      <c r="E59" s="46"/>
-      <c r="F59" s="28"/>
-      <c r="G59" s="28"/>
-      <c r="H59" s="46"/>
-      <c r="I59" s="29"/>
-      <c r="J59" s="30"/>
+      <c r="B59" s="38"/>
+      <c r="C59" s="46"/>
+      <c r="D59" s="16"/>
+      <c r="E59" s="41"/>
+      <c r="F59" s="23"/>
+      <c r="G59" s="23"/>
+      <c r="H59" s="41"/>
+      <c r="I59" s="24"/>
+      <c r="J59" s="25"/>
     </row>
     <row r="60" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B60" s="44"/>
-      <c r="C60" s="54"/>
-      <c r="D60" s="36"/>
-      <c r="E60" s="47"/>
-      <c r="F60" s="35"/>
-      <c r="G60" s="35"/>
-      <c r="H60" s="47"/>
-      <c r="I60" s="37"/>
-      <c r="J60" s="38"/>
+      <c r="B60" s="39"/>
+      <c r="C60" s="46"/>
+      <c r="D60" s="16"/>
+      <c r="E60" s="41"/>
+      <c r="F60" s="23"/>
+      <c r="G60" s="23"/>
+      <c r="H60" s="41"/>
+      <c r="I60" s="24"/>
+      <c r="J60" s="25"/>
     </row>
     <row r="61" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B61" s="43"/>
-      <c r="C61" s="53"/>
-      <c r="D61" s="21"/>
-      <c r="E61" s="46"/>
-      <c r="F61" s="28"/>
-      <c r="G61" s="28"/>
-      <c r="H61" s="46"/>
-      <c r="I61" s="29"/>
-      <c r="J61" s="30"/>
+      <c r="B61" s="38"/>
+      <c r="C61" s="46"/>
+      <c r="D61" s="16"/>
+      <c r="E61" s="41"/>
+      <c r="F61" s="23"/>
+      <c r="G61" s="23"/>
+      <c r="H61" s="41"/>
+      <c r="I61" s="24"/>
+      <c r="J61" s="25"/>
     </row>
     <row r="62" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B62" s="43"/>
-      <c r="C62" s="53"/>
-      <c r="D62" s="21"/>
-      <c r="E62" s="46"/>
-      <c r="F62" s="28"/>
-      <c r="G62" s="28"/>
-      <c r="H62" s="46"/>
-      <c r="I62" s="29"/>
-      <c r="J62" s="30"/>
+      <c r="B62" s="38"/>
+      <c r="C62" s="46"/>
+      <c r="D62" s="16"/>
+      <c r="E62" s="41"/>
+      <c r="F62" s="23"/>
+      <c r="G62" s="23"/>
+      <c r="H62" s="41"/>
+      <c r="I62" s="24"/>
+      <c r="J62" s="25"/>
     </row>
     <row r="63" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B63" s="43"/>
-      <c r="C63" s="53"/>
-      <c r="D63" s="21"/>
-      <c r="E63" s="46"/>
-      <c r="F63" s="28"/>
-      <c r="G63" s="28"/>
-      <c r="H63" s="46"/>
-      <c r="I63" s="29"/>
-      <c r="J63" s="30"/>
+      <c r="B63" s="38"/>
+      <c r="C63" s="46"/>
+      <c r="D63" s="16"/>
+      <c r="E63" s="41"/>
+      <c r="F63" s="23"/>
+      <c r="G63" s="23"/>
+      <c r="H63" s="41"/>
+      <c r="I63" s="24"/>
+      <c r="J63" s="25"/>
     </row>
     <row r="64" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B64" s="43"/>
-      <c r="C64" s="53"/>
-      <c r="D64" s="21"/>
-      <c r="E64" s="46"/>
-      <c r="F64" s="28"/>
-      <c r="G64" s="28"/>
-      <c r="H64" s="46"/>
-      <c r="I64" s="29"/>
-      <c r="J64" s="30"/>
+      <c r="B64" s="38"/>
+      <c r="C64" s="46"/>
+      <c r="D64" s="16"/>
+      <c r="E64" s="41"/>
+      <c r="F64" s="23"/>
+      <c r="G64" s="23"/>
+      <c r="H64" s="41"/>
+      <c r="I64" s="24"/>
+      <c r="J64" s="25"/>
     </row>
     <row r="65" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B65" s="43"/>
-      <c r="C65" s="53"/>
-      <c r="D65" s="21"/>
-      <c r="E65" s="46"/>
-      <c r="F65" s="28"/>
-      <c r="G65" s="28"/>
-      <c r="H65" s="46"/>
-      <c r="I65" s="29"/>
-      <c r="J65" s="30"/>
+      <c r="B65" s="38"/>
+      <c r="C65" s="46"/>
+      <c r="D65" s="16"/>
+      <c r="E65" s="41"/>
+      <c r="F65" s="23"/>
+      <c r="G65" s="23"/>
+      <c r="H65" s="41"/>
+      <c r="I65" s="24"/>
+      <c r="J65" s="25"/>
     </row>
     <row r="66" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B66" s="43"/>
-      <c r="C66" s="53"/>
-      <c r="D66" s="21"/>
-      <c r="E66" s="46"/>
-      <c r="F66" s="28"/>
-      <c r="G66" s="28"/>
-      <c r="H66" s="46"/>
-      <c r="I66" s="29"/>
-      <c r="J66" s="30"/>
+      <c r="B66" s="38"/>
+      <c r="C66" s="46"/>
+      <c r="D66" s="16"/>
+      <c r="E66" s="41"/>
+      <c r="F66" s="23"/>
+      <c r="G66" s="23"/>
+      <c r="H66" s="41"/>
+      <c r="I66" s="24"/>
+      <c r="J66" s="25"/>
     </row>
     <row r="67" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B67" s="43"/>
-      <c r="C67" s="53"/>
-      <c r="D67" s="21"/>
-      <c r="E67" s="46"/>
-      <c r="F67" s="28"/>
-      <c r="G67" s="28"/>
-      <c r="H67" s="46"/>
-      <c r="I67" s="29"/>
-      <c r="J67" s="30"/>
+      <c r="B67" s="38"/>
+      <c r="C67" s="46"/>
+      <c r="D67" s="16"/>
+      <c r="E67" s="41"/>
+      <c r="F67" s="23"/>
+      <c r="G67" s="23"/>
+      <c r="H67" s="41"/>
+      <c r="I67" s="24"/>
+      <c r="J67" s="25"/>
     </row>
     <row r="68" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B68" s="43"/>
-      <c r="C68" s="53"/>
-      <c r="D68" s="21"/>
-      <c r="E68" s="46"/>
-      <c r="F68" s="28"/>
-      <c r="G68" s="28"/>
-      <c r="H68" s="46"/>
-      <c r="I68" s="29"/>
-      <c r="J68" s="30"/>
+      <c r="B68" s="38"/>
+      <c r="C68" s="48"/>
+      <c r="D68" s="27"/>
+      <c r="E68" s="43"/>
+      <c r="F68" s="26"/>
+      <c r="G68" s="26"/>
+      <c r="H68" s="43"/>
+      <c r="I68" s="28"/>
+      <c r="J68" s="29"/>
     </row>
     <row r="69" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B69" s="43"/>
-      <c r="C69" s="53"/>
-      <c r="D69" s="21"/>
-      <c r="E69" s="46"/>
-      <c r="F69" s="28"/>
-      <c r="G69" s="28"/>
-      <c r="H69" s="46"/>
-      <c r="I69" s="29"/>
-      <c r="J69" s="30"/>
+      <c r="B69" s="38"/>
     </row>
     <row r="70" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B70" s="45"/>
-      <c r="C70" s="55"/>
-      <c r="D70" s="32"/>
-      <c r="E70" s="48"/>
-      <c r="F70" s="31"/>
-      <c r="G70" s="31"/>
-      <c r="H70" s="48"/>
-      <c r="I70" s="33"/>
-      <c r="J70" s="34"/>
+      <c r="B70" s="40"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -2321,10 +2384,10 @@
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E8:E70" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E14:E68">
       <formula1>"Alta, Media, Baja"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H8:H70" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H8:H68">
       <formula1>"Abierto, Cerrado, En Espera"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2344,7 +2407,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B37"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
@@ -2507,62 +2570,10 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10001</Type>
-    <SequenceNumber>1000</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=15.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10002</Type>
-    <SequenceNumber>1001</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=15.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10004</Type>
-    <SequenceNumber>1002</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=15.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10006</Type>
-    <SequenceNumber>1003</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=15.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-</spe:Receivers>
+<LongProperties xmlns="http://schemas.microsoft.com/office/2006/metadata/longProperties"/>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A5124E24CAF14D46B2DD609ACFD84C07" ma:contentTypeVersion="0" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="9971b3b784abbe199b171e233c6d3889">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="01eb4bd6-a8ff-4439-b7eb-fe0a650fbd8a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9a36e787f936117f0a8f63b0cc0186e7" ns2:_="">
     <xsd:import namespace="01eb4bd6-a8ff-4439-b7eb-fe0a650fbd8a"/>
@@ -2707,8 +2718,60 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/item5.xml><?xml version="1.0" encoding="utf-8"?>
-<LongProperties xmlns="http://schemas.microsoft.com/office/2006/metadata/longProperties"/>
+<?mso-contentType ?>
+<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10001</Type>
+    <SequenceNumber>1000</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=15.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10002</Type>
+    <SequenceNumber>1001</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=15.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10004</Type>
+    <SequenceNumber>1002</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=15.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10006</Type>
+    <SequenceNumber>1003</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=15.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+</spe:Receivers>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2720,30 +2783,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{93598FFC-8BC8-4FB2-AD2B-08B9103F4BFD}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B4C90E1D-E05D-455D-968E-447D81ECDDDE}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/events"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/longProperties"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{14995395-6027-48F9-B63A-D36F3BD77631}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="01eb4bd6-a8ff-4439-b7eb-fe0a650fbd8a"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{05E9CE14-C54D-4014-8F1A-0EF9F4DD6863}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2761,10 +2808,26 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{14995395-6027-48F9-B63A-D36F3BD77631}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="01eb4bd6-a8ff-4439-b7eb-fe0a650fbd8a"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps5.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B4C90E1D-E05D-455D-968E-447D81ECDDDE}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{93598FFC-8BC8-4FB2-AD2B-08B9103F4BFD}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/longProperties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/events"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>